--- a/data/Persentase_Penduduk_Miskin_dengan_Kode.xlsx
+++ b/data/Persentase_Penduduk_Miskin_dengan_Kode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ff7feecb1f6e1f94/Documents/Materi Kuliah/Visualisasi Data/Deploy Web UAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{1696A676-F2FE-4F59-A248-A74A7ED172C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89D59D8A-6BD8-4B2B-8744-DEA9EEDC36AE}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{1696A676-F2FE-4F59-A248-A74A7ED172C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C4750E-C717-4BAE-95A8-C4F0EA32AD5E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="1065">
   <si>
     <t>Provinsi/Kabupaten/Kota</t>
   </si>
@@ -3265,10 +3265,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3284,6 +3282,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3608,7 +3610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J515"/>
+  <dimension ref="A1:G515"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -3616,30 +3618,30 @@
     <col min="3" max="6" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1064</v>
       </c>
       <c r="B1" t="s">
         <v>1063</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="3">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="3">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="3">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3661,11 +3663,8 @@
       <c r="G2" s="1">
         <v>15.52</v>
       </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3688,7 +3687,7 @@
         <v>17.07</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -3711,7 +3710,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3734,7 +3733,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>11.24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3780,7 +3779,7 @@
         <v>12.29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3803,7 +3802,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3826,7 +3825,7 @@
         <v>11.05</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3849,7 +3848,7 @@
         <v>16.46</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -3872,7 +3871,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -3895,7 +3894,7 @@
         <v>14.27</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -3918,7 +3917,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3941,7 +3940,7 @@
         <v>16.77</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -3964,7 +3963,7 @@
         <v>10.84</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -15466,6 +15465,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -15475,18 +15477,18 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
+      <c r="A2" s="2"/>
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>2</v>
       </c>
